--- a/final_data_pipeline/output/311224longform.xlsx
+++ b/final_data_pipeline/output/311224longform.xlsx
@@ -1095,7 +1095,7 @@
         <v>172</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -1184,7 +1184,7 @@
         <v>172</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1273,7 +1273,7 @@
         <v>172</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1362,7 +1362,7 @@
         <v>172</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1451,7 +1451,7 @@
         <v>172</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1540,7 +1540,7 @@
         <v>172</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1629,7 +1629,7 @@
         <v>172</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1721,7 +1721,7 @@
         <v>172</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1810,7 +1810,7 @@
         <v>172</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1899,7 +1899,7 @@
         <v>172</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1988,7 +1988,7 @@
         <v>172</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -2077,7 +2077,7 @@
         <v>172</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -2166,7 +2166,7 @@
         <v>172</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2255,7 +2255,7 @@
         <v>172</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2347,7 +2347,7 @@
         <v>172</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2436,7 +2436,7 @@
         <v>172</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2528,7 +2528,7 @@
         <v>172</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2617,7 +2617,7 @@
         <v>172</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2706,7 +2706,7 @@
         <v>172</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2795,7 +2795,7 @@
         <v>172</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -4228,7 +4228,7 @@
         <v>172</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB37">
         <v>8000</v>
@@ -4317,7 +4317,7 @@
         <v>172</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4406,7 +4406,7 @@
         <v>172</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4498,7 +4498,7 @@
         <v>172</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4590,7 +4590,7 @@
         <v>172</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4679,7 +4679,7 @@
         <v>172</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4768,7 +4768,7 @@
         <v>172</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4857,7 +4857,7 @@
         <v>172</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4946,7 +4946,7 @@
         <v>172</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -5035,7 +5035,7 @@
         <v>172</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -5572,7 +5572,7 @@
         <v>172</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5664,7 +5664,7 @@
         <v>172</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5753,7 +5753,7 @@
         <v>172</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5842,7 +5842,7 @@
         <v>172</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5931,7 +5931,7 @@
         <v>172</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -6020,7 +6020,7 @@
         <v>172</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB57">
         <v>8000</v>
@@ -6109,7 +6109,7 @@
         <v>172</v>
       </c>
       <c r="AA58">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB58">
         <v>8000</v>
@@ -6198,7 +6198,7 @@
         <v>172</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6287,7 +6287,7 @@
         <v>172</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6376,7 +6376,7 @@
         <v>172</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6465,7 +6465,7 @@
         <v>172</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6554,7 +6554,7 @@
         <v>172</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6646,7 +6646,7 @@
         <v>172</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6738,7 +6738,7 @@
         <v>172</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6827,7 +6827,7 @@
         <v>172</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6916,7 +6916,7 @@
         <v>172</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -7005,7 +7005,7 @@
         <v>172</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -7094,7 +7094,7 @@
         <v>172</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -7183,7 +7183,7 @@
         <v>172</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -7272,7 +7272,7 @@
         <v>172</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7361,7 +7361,7 @@
         <v>172</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7450,7 +7450,7 @@
         <v>172</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7542,7 +7542,7 @@
         <v>172</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7634,7 +7634,7 @@
         <v>172</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7723,7 +7723,7 @@
         <v>172</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -8260,7 +8260,7 @@
         <v>172</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -8349,7 +8349,7 @@
         <v>172</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -8441,7 +8441,7 @@
         <v>172</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8530,7 +8530,7 @@
         <v>172</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8619,7 +8619,7 @@
         <v>172</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -9604,7 +9604,7 @@
         <v>172</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9696,7 +9696,7 @@
         <v>172</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9785,7 +9785,7 @@
         <v>172</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9874,7 +9874,7 @@
         <v>172</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9963,7 +9963,7 @@
         <v>172</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>16.97685185185183</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -10052,7 +10052,7 @@
         <v>172</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -10144,7 +10144,7 @@
         <v>172</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -10233,7 +10233,7 @@
         <v>172</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10322,7 +10322,7 @@
         <v>172</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10411,7 +10411,7 @@
         <v>172</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>-3.847222222222223</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -11396,7 +11396,7 @@
         <v>172</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11488,7 +11488,7 @@
         <v>172</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -11577,7 +11577,7 @@
         <v>172</v>
       </c>
       <c r="AA119">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB119">
         <v>8000</v>
@@ -11666,7 +11666,7 @@
         <v>172</v>
       </c>
       <c r="AA120">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB120">
         <v>8000</v>
@@ -11755,7 +11755,7 @@
         <v>172</v>
       </c>
       <c r="AA121">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB121">
         <v>8000</v>
@@ -11844,7 +11844,7 @@
         <v>172</v>
       </c>
       <c r="AA122">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB122">
         <v>8000</v>
@@ -11933,7 +11933,7 @@
         <v>172</v>
       </c>
       <c r="AA123">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB123">
         <v>8000</v>
@@ -12022,7 +12022,7 @@
         <v>172</v>
       </c>
       <c r="AA124">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB124">
         <v>8000</v>
@@ -12111,7 +12111,7 @@
         <v>172</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12203,7 +12203,7 @@
         <v>172</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -12740,7 +12740,7 @@
         <v>172</v>
       </c>
       <c r="AA132">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB132">
         <v>8000</v>
@@ -12832,7 +12832,7 @@
         <v>172</v>
       </c>
       <c r="AA133">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB133">
         <v>8000</v>
@@ -12921,7 +12921,7 @@
         <v>172</v>
       </c>
       <c r="AA134">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB134">
         <v>8000</v>
@@ -13010,7 +13010,7 @@
         <v>172</v>
       </c>
       <c r="AA135">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB135">
         <v>8000</v>
@@ -13099,7 +13099,7 @@
         <v>172</v>
       </c>
       <c r="AA136">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="AB136">
         <v>8000</v>
@@ -13188,7 +13188,7 @@
         <v>172</v>
       </c>
       <c r="AA137">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB137">
         <v>8000</v>
@@ -13277,7 +13277,7 @@
         <v>172</v>
       </c>
       <c r="AA138">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB138">
         <v>8000</v>
@@ -13366,7 +13366,7 @@
         <v>172</v>
       </c>
       <c r="AA139">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB139">
         <v>8000</v>
@@ -13458,7 +13458,7 @@
         <v>172</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -13547,7 +13547,7 @@
         <v>172</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -13636,7 +13636,7 @@
         <v>172</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -13728,7 +13728,7 @@
         <v>172</v>
       </c>
       <c r="AA143">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB143">
         <v>8000</v>
@@ -13817,7 +13817,7 @@
         <v>172</v>
       </c>
       <c r="AA144">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB144">
         <v>8000</v>
@@ -13906,7 +13906,7 @@
         <v>172</v>
       </c>
       <c r="AA145">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB145">
         <v>8000</v>
@@ -13995,7 +13995,7 @@
         <v>172</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -14084,7 +14084,7 @@
         <v>172</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -14176,7 +14176,7 @@
         <v>172</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -14265,7 +14265,7 @@
         <v>172</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -14354,7 +14354,7 @@
         <v>172</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -14443,7 +14443,7 @@
         <v>172</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -17220,7 +17220,7 @@
         <v>172</v>
       </c>
       <c r="AA182">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB182">
         <v>8000</v>
@@ -17309,7 +17309,7 @@
         <v>172</v>
       </c>
       <c r="AA183">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB183">
         <v>8000</v>
@@ -17398,7 +17398,7 @@
         <v>172</v>
       </c>
       <c r="AA184">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB184">
         <v>8000</v>
@@ -17487,7 +17487,7 @@
         <v>172</v>
       </c>
       <c r="AA185">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB185">
         <v>8000</v>
@@ -17576,7 +17576,7 @@
         <v>172</v>
       </c>
       <c r="AA186">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB186">
         <v>8000</v>
@@ -17668,7 +17668,7 @@
         <v>172</v>
       </c>
       <c r="AA187">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB187">
         <v>8000</v>
@@ -17760,7 +17760,7 @@
         <v>172</v>
       </c>
       <c r="AA188">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB188">
         <v>8000</v>
@@ -17849,7 +17849,7 @@
         <v>172</v>
       </c>
       <c r="AA189">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB189">
         <v>8000</v>
@@ -17938,7 +17938,7 @@
         <v>172</v>
       </c>
       <c r="AA190">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB190">
         <v>8000</v>
@@ -18027,7 +18027,7 @@
         <v>172</v>
       </c>
       <c r="AA191">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB191">
         <v>8000</v>
@@ -18116,7 +18116,7 @@
         <v>172</v>
       </c>
       <c r="AA192">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB192">
         <v>8000</v>
@@ -18205,7 +18205,7 @@
         <v>172</v>
       </c>
       <c r="AA193">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB193">
         <v>8000</v>
@@ -18294,7 +18294,7 @@
         <v>172</v>
       </c>
       <c r="AA194">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB194">
         <v>8000</v>
@@ -18386,7 +18386,7 @@
         <v>172</v>
       </c>
       <c r="AA195">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB195">
         <v>8000</v>
@@ -18478,7 +18478,7 @@
         <v>172</v>
       </c>
       <c r="AA196">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB196">
         <v>8000</v>
@@ -18567,7 +18567,7 @@
         <v>172</v>
       </c>
       <c r="AA197">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB197">
         <v>8000</v>
@@ -18656,7 +18656,7 @@
         <v>172</v>
       </c>
       <c r="AA198">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB198">
         <v>8000</v>
@@ -18745,7 +18745,7 @@
         <v>172</v>
       </c>
       <c r="AA199">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB199">
         <v>8000</v>
@@ -18834,7 +18834,7 @@
         <v>172</v>
       </c>
       <c r="AA200">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB200">
         <v>8000</v>
@@ -18923,7 +18923,7 @@
         <v>172</v>
       </c>
       <c r="AA201">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AB201">
         <v>8000</v>
@@ -19463,7 +19463,7 @@
         <v>172</v>
       </c>
       <c r="AA207">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB207">
         <v>8000</v>
@@ -19552,7 +19552,7 @@
         <v>172</v>
       </c>
       <c r="AA208">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB208">
         <v>8000</v>
@@ -19644,7 +19644,7 @@
         <v>172</v>
       </c>
       <c r="AA209">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB209">
         <v>8000</v>
@@ -19733,7 +19733,7 @@
         <v>172</v>
       </c>
       <c r="AA210">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB210">
         <v>8000</v>
@@ -19828,7 +19828,7 @@
         <v>172</v>
       </c>
       <c r="AA211">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB211">
         <v>8000</v>
@@ -19917,7 +19917,7 @@
         <v>172</v>
       </c>
       <c r="AA212">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB212">
         <v>8000</v>
@@ -20006,7 +20006,7 @@
         <v>172</v>
       </c>
       <c r="AA213">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB213">
         <v>8000</v>
@@ -20095,7 +20095,7 @@
         <v>172</v>
       </c>
       <c r="AA214">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB214">
         <v>8000</v>
@@ -20184,7 +20184,7 @@
         <v>172</v>
       </c>
       <c r="AA215">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB215">
         <v>8000</v>
@@ -20273,7 +20273,7 @@
         <v>172</v>
       </c>
       <c r="AA216">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB216">
         <v>8000</v>
@@ -20362,7 +20362,7 @@
         <v>172</v>
       </c>
       <c r="AA217">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB217">
         <v>8000</v>
@@ -20451,7 +20451,7 @@
         <v>172</v>
       </c>
       <c r="AA218">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB218">
         <v>8000</v>
@@ -20540,7 +20540,7 @@
         <v>172</v>
       </c>
       <c r="AA219">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB219">
         <v>8000</v>
@@ -20629,7 +20629,7 @@
         <v>172</v>
       </c>
       <c r="AA220">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB220">
         <v>8000</v>
@@ -20721,7 +20721,7 @@
         <v>172</v>
       </c>
       <c r="AA221">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB221">
         <v>8000</v>
@@ -20810,7 +20810,7 @@
         <v>172</v>
       </c>
       <c r="AA222">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB222">
         <v>8000</v>
@@ -20899,7 +20899,7 @@
         <v>172</v>
       </c>
       <c r="AA223">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB223">
         <v>8000</v>
@@ -20988,7 +20988,7 @@
         <v>172</v>
       </c>
       <c r="AA224">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB224">
         <v>8000</v>
@@ -21080,7 +21080,7 @@
         <v>172</v>
       </c>
       <c r="AA225">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB225">
         <v>8000</v>
@@ -21169,7 +21169,7 @@
         <v>172</v>
       </c>
       <c r="AA226">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB226">
         <v>8000</v>
@@ -21258,7 +21258,7 @@
         <v>172</v>
       </c>
       <c r="AA227">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB227">
         <v>8000</v>
@@ -21353,7 +21353,7 @@
         <v>172</v>
       </c>
       <c r="AA228">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB228">
         <v>8000</v>
@@ -21445,7 +21445,7 @@
         <v>172</v>
       </c>
       <c r="AA229">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB229">
         <v>8000</v>
@@ -21537,7 +21537,7 @@
         <v>172</v>
       </c>
       <c r="AA230">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB230">
         <v>8000</v>
@@ -21626,7 +21626,7 @@
         <v>172</v>
       </c>
       <c r="AA231">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB231">
         <v>8000</v>
@@ -21715,7 +21715,7 @@
         <v>172</v>
       </c>
       <c r="AA232">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB232">
         <v>8000</v>
@@ -21804,7 +21804,7 @@
         <v>172</v>
       </c>
       <c r="AA233">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB233">
         <v>8000</v>
@@ -21893,7 +21893,7 @@
         <v>172</v>
       </c>
       <c r="AA234">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB234">
         <v>8000</v>
@@ -21982,7 +21982,7 @@
         <v>172</v>
       </c>
       <c r="AA235">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB235">
         <v>8000</v>
@@ -22071,7 +22071,7 @@
         <v>172</v>
       </c>
       <c r="AA236">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB236">
         <v>8000</v>
@@ -22160,7 +22160,7 @@
         <v>172</v>
       </c>
       <c r="AA237">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB237">
         <v>8000</v>
@@ -22249,7 +22249,7 @@
         <v>172</v>
       </c>
       <c r="AA238">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB238">
         <v>8000</v>
@@ -22338,7 +22338,7 @@
         <v>172</v>
       </c>
       <c r="AA239">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB239">
         <v>8000</v>
@@ -22427,7 +22427,7 @@
         <v>172</v>
       </c>
       <c r="AA240">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB240">
         <v>8000</v>
@@ -22516,7 +22516,7 @@
         <v>172</v>
       </c>
       <c r="AA241">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB241">
         <v>8000</v>
@@ -22605,7 +22605,7 @@
         <v>172</v>
       </c>
       <c r="AA242">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB242">
         <v>8000</v>
@@ -22694,7 +22694,7 @@
         <v>172</v>
       </c>
       <c r="AA243">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB243">
         <v>8000</v>
@@ -22783,7 +22783,7 @@
         <v>172</v>
       </c>
       <c r="AA244">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB244">
         <v>8000</v>
@@ -22872,7 +22872,7 @@
         <v>172</v>
       </c>
       <c r="AA245">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB245">
         <v>8000</v>
@@ -22961,7 +22961,7 @@
         <v>172</v>
       </c>
       <c r="AA246">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB246">
         <v>8000</v>
@@ -23050,7 +23050,7 @@
         <v>172</v>
       </c>
       <c r="AA247">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB247">
         <v>8000</v>
@@ -23139,7 +23139,7 @@
         <v>172</v>
       </c>
       <c r="AA248">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB248">
         <v>8000</v>
@@ -23228,7 +23228,7 @@
         <v>172</v>
       </c>
       <c r="AA249">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB249">
         <v>8000</v>
@@ -23317,7 +23317,7 @@
         <v>172</v>
       </c>
       <c r="AA250">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB250">
         <v>8000</v>
@@ -23406,7 +23406,7 @@
         <v>172</v>
       </c>
       <c r="AA251">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB251">
         <v>8000</v>
@@ -23495,7 +23495,7 @@
         <v>172</v>
       </c>
       <c r="AA252">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB252">
         <v>8000</v>
@@ -23587,7 +23587,7 @@
         <v>172</v>
       </c>
       <c r="AA253">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB253">
         <v>8000</v>
@@ -23679,7 +23679,7 @@
         <v>172</v>
       </c>
       <c r="AA254">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB254">
         <v>8000</v>
@@ -23768,7 +23768,7 @@
         <v>172</v>
       </c>
       <c r="AA255">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB255">
         <v>8000</v>
@@ -23860,7 +23860,7 @@
         <v>172</v>
       </c>
       <c r="AA256">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB256">
         <v>8000</v>
@@ -23949,7 +23949,7 @@
         <v>172</v>
       </c>
       <c r="AA257">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB257">
         <v>8000</v>
@@ -24041,7 +24041,7 @@
         <v>172</v>
       </c>
       <c r="AA258">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AB258">
         <v>8000</v>
@@ -25026,7 +25026,7 @@
         <v>172</v>
       </c>
       <c r="AA269">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB269">
         <v>8000</v>
@@ -25115,7 +25115,7 @@
         <v>172</v>
       </c>
       <c r="AA270">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB270">
         <v>8000</v>
@@ -25204,7 +25204,7 @@
         <v>172</v>
       </c>
       <c r="AA271">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB271">
         <v>8000</v>
@@ -25293,7 +25293,7 @@
         <v>172</v>
       </c>
       <c r="AA272">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB272">
         <v>8000</v>
@@ -25385,7 +25385,7 @@
         <v>172</v>
       </c>
       <c r="AA273">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB273">
         <v>8000</v>
@@ -25477,7 +25477,7 @@
         <v>172</v>
       </c>
       <c r="AA274">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB274">
         <v>8000</v>
@@ -25566,7 +25566,7 @@
         <v>172</v>
       </c>
       <c r="AA275">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB275">
         <v>8000</v>
@@ -25655,7 +25655,7 @@
         <v>172</v>
       </c>
       <c r="AA276">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB276">
         <v>8000</v>
@@ -25744,7 +25744,7 @@
         <v>172</v>
       </c>
       <c r="AA277">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB277">
         <v>8000</v>
@@ -25833,7 +25833,7 @@
         <v>172</v>
       </c>
       <c r="AA278">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB278">
         <v>8000</v>
@@ -25922,7 +25922,7 @@
         <v>172</v>
       </c>
       <c r="AA279">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB279">
         <v>8000</v>
@@ -26011,7 +26011,7 @@
         <v>172</v>
       </c>
       <c r="AA280">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB280">
         <v>8000</v>
@@ -26100,7 +26100,7 @@
         <v>172</v>
       </c>
       <c r="AA281">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB281">
         <v>8000</v>
@@ -26189,7 +26189,7 @@
         <v>172</v>
       </c>
       <c r="AA282">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB282">
         <v>8000</v>
@@ -26281,7 +26281,7 @@
         <v>172</v>
       </c>
       <c r="AA283">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB283">
         <v>8000</v>
@@ -26370,7 +26370,7 @@
         <v>172</v>
       </c>
       <c r="AA284">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB284">
         <v>8000</v>
@@ -26462,7 +26462,7 @@
         <v>172</v>
       </c>
       <c r="AA285">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB285">
         <v>8000</v>
@@ -26551,7 +26551,7 @@
         <v>172</v>
       </c>
       <c r="AA286">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB286">
         <v>8000</v>
@@ -26640,7 +26640,7 @@
         <v>172</v>
       </c>
       <c r="AA287">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB287">
         <v>8000</v>
@@ -26729,7 +26729,7 @@
         <v>172</v>
       </c>
       <c r="AA288">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AB288">
         <v>8000</v>
@@ -26818,7 +26818,7 @@
         <v>172</v>
       </c>
       <c r="AA289">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB289">
         <v>8000</v>
@@ -26907,7 +26907,7 @@
         <v>172</v>
       </c>
       <c r="AA290">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB290">
         <v>8000</v>
@@ -26996,7 +26996,7 @@
         <v>172</v>
       </c>
       <c r="AA291">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB291">
         <v>8000</v>
@@ -27085,7 +27085,7 @@
         <v>172</v>
       </c>
       <c r="AA292">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB292">
         <v>8000</v>
@@ -27174,7 +27174,7 @@
         <v>172</v>
       </c>
       <c r="AA293">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB293">
         <v>8000</v>
@@ -27263,7 +27263,7 @@
         <v>172</v>
       </c>
       <c r="AA294">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB294">
         <v>8000</v>
@@ -27355,7 +27355,7 @@
         <v>172</v>
       </c>
       <c r="AA295">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB295">
         <v>8000</v>
@@ -27447,7 +27447,7 @@
         <v>172</v>
       </c>
       <c r="AA296">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB296">
         <v>8000</v>
@@ -27539,7 +27539,7 @@
         <v>172</v>
       </c>
       <c r="AA297">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB297">
         <v>8000</v>
@@ -27631,7 +27631,7 @@
         <v>172</v>
       </c>
       <c r="AA298">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB298">
         <v>8000</v>
@@ -27720,7 +27720,7 @@
         <v>172</v>
       </c>
       <c r="AA299">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB299">
         <v>8000</v>
@@ -27815,7 +27815,7 @@
         <v>172</v>
       </c>
       <c r="AA300">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB300">
         <v>8000</v>
@@ -27904,7 +27904,7 @@
         <v>172</v>
       </c>
       <c r="AA301">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB301">
         <v>8000</v>
@@ -27993,7 +27993,7 @@
         <v>172</v>
       </c>
       <c r="AA302">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB302">
         <v>8000</v>
@@ -28082,7 +28082,7 @@
         <v>172</v>
       </c>
       <c r="AA303">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB303">
         <v>8000</v>
@@ -28174,7 +28174,7 @@
         <v>172</v>
       </c>
       <c r="AA304">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB304">
         <v>8000</v>
@@ -28263,7 +28263,7 @@
         <v>172</v>
       </c>
       <c r="AA305">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB305">
         <v>8000</v>
@@ -28352,7 +28352,7 @@
         <v>172</v>
       </c>
       <c r="AA306">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB306">
         <v>8000</v>
@@ -28441,7 +28441,7 @@
         <v>172</v>
       </c>
       <c r="AA307">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB307">
         <v>8000</v>
@@ -28530,7 +28530,7 @@
         <v>172</v>
       </c>
       <c r="AA308">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB308">
         <v>8000</v>
@@ -28619,7 +28619,7 @@
         <v>172</v>
       </c>
       <c r="AA309">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB309">
         <v>8000</v>
@@ -28708,7 +28708,7 @@
         <v>172</v>
       </c>
       <c r="AA310">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB310">
         <v>8000</v>
@@ -28797,7 +28797,7 @@
         <v>172</v>
       </c>
       <c r="AA311">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB311">
         <v>8000</v>
@@ -28886,7 +28886,7 @@
         <v>172</v>
       </c>
       <c r="AA312">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB312">
         <v>8000</v>
@@ -28975,7 +28975,7 @@
         <v>172</v>
       </c>
       <c r="AA313">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB313">
         <v>8000</v>
@@ -29064,7 +29064,7 @@
         <v>172</v>
       </c>
       <c r="AA314">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AB314">
         <v>8000</v>
@@ -29601,7 +29601,7 @@
         <v>172</v>
       </c>
       <c r="AA320">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB320">
         <v>8000</v>
@@ -29690,7 +29690,7 @@
         <v>172</v>
       </c>
       <c r="AA321">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB321">
         <v>8000</v>
@@ -29779,7 +29779,7 @@
         <v>172</v>
       </c>
       <c r="AA322">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB322">
         <v>8000</v>
@@ -29868,7 +29868,7 @@
         <v>172</v>
       </c>
       <c r="AA323">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB323">
         <v>8000</v>
@@ -29960,7 +29960,7 @@
         <v>172</v>
       </c>
       <c r="AA324">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AB324">
         <v>8000</v>
@@ -30945,7 +30945,7 @@
         <v>172</v>
       </c>
       <c r="AA335">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB335">
         <v>8000</v>
@@ -31034,7 +31034,7 @@
         <v>172</v>
       </c>
       <c r="AA336">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB336">
         <v>8000</v>
@@ -31123,7 +31123,7 @@
         <v>172</v>
       </c>
       <c r="AA337">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB337">
         <v>8000</v>
@@ -31212,7 +31212,7 @@
         <v>172</v>
       </c>
       <c r="AA338">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB338">
         <v>8000</v>
@@ -31301,7 +31301,7 @@
         <v>172</v>
       </c>
       <c r="AA339">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB339">
         <v>8000</v>
@@ -31390,7 +31390,7 @@
         <v>172</v>
       </c>
       <c r="AA340">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB340">
         <v>8000</v>
@@ -31479,7 +31479,7 @@
         <v>172</v>
       </c>
       <c r="AA341">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB341">
         <v>8000</v>
@@ -31568,7 +31568,7 @@
         <v>172</v>
       </c>
       <c r="AA342">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB342">
         <v>8000</v>
@@ -31657,7 +31657,7 @@
         <v>172</v>
       </c>
       <c r="AA343">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB343">
         <v>8000</v>
@@ -31746,7 +31746,7 @@
         <v>172</v>
       </c>
       <c r="AA344">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB344">
         <v>8000</v>
@@ -31838,7 +31838,7 @@
         <v>172</v>
       </c>
       <c r="AA345">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB345">
         <v>8000</v>
@@ -31927,7 +31927,7 @@
         <v>172</v>
       </c>
       <c r="AA346">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB346">
         <v>8000</v>
@@ -32016,7 +32016,7 @@
         <v>172</v>
       </c>
       <c r="AA347">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB347">
         <v>8000</v>
@@ -32105,7 +32105,7 @@
         <v>172</v>
       </c>
       <c r="AA348">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB348">
         <v>8000</v>
@@ -32197,7 +32197,7 @@
         <v>172</v>
       </c>
       <c r="AA349">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB349">
         <v>8000</v>
@@ -32289,7 +32289,7 @@
         <v>172</v>
       </c>
       <c r="AA350">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB350">
         <v>8000</v>
@@ -32381,7 +32381,7 @@
         <v>172</v>
       </c>
       <c r="AA351">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB351">
         <v>8000</v>
@@ -32470,7 +32470,7 @@
         <v>172</v>
       </c>
       <c r="AA352">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB352">
         <v>8000</v>
@@ -32562,7 +32562,7 @@
         <v>172</v>
       </c>
       <c r="AA353">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB353">
         <v>8000</v>
@@ -32651,7 +32651,7 @@
         <v>172</v>
       </c>
       <c r="AA354">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB354">
         <v>8000</v>
@@ -32740,7 +32740,7 @@
         <v>172</v>
       </c>
       <c r="AA355">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB355">
         <v>8000</v>
@@ -32829,7 +32829,7 @@
         <v>172</v>
       </c>
       <c r="AA356">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB356">
         <v>8000</v>
@@ -32918,7 +32918,7 @@
         <v>172</v>
       </c>
       <c r="AA357">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB357">
         <v>8000</v>
@@ -33007,7 +33007,7 @@
         <v>172</v>
       </c>
       <c r="AA358">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB358">
         <v>8000</v>
@@ -33096,7 +33096,7 @@
         <v>172</v>
       </c>
       <c r="AA359">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB359">
         <v>8000</v>
@@ -34529,7 +34529,7 @@
         <v>172</v>
       </c>
       <c r="AA375">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB375">
         <v>8000</v>
@@ -34621,7 +34621,7 @@
         <v>172</v>
       </c>
       <c r="AA376">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB376">
         <v>8000</v>
@@ -34710,7 +34710,7 @@
         <v>172</v>
       </c>
       <c r="AA377">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB377">
         <v>8000</v>
@@ -34799,7 +34799,7 @@
         <v>172</v>
       </c>
       <c r="AA378">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB378">
         <v>8000</v>
@@ -34888,7 +34888,7 @@
         <v>172</v>
       </c>
       <c r="AA379">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB379">
         <v>8000</v>
@@ -34977,7 +34977,7 @@
         <v>172</v>
       </c>
       <c r="AA380">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB380">
         <v>8000</v>
@@ -35069,7 +35069,7 @@
         <v>172</v>
       </c>
       <c r="AA381">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB381">
         <v>8000</v>
@@ -35158,7 +35158,7 @@
         <v>172</v>
       </c>
       <c r="AA382">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB382">
         <v>8000</v>
@@ -35247,7 +35247,7 @@
         <v>172</v>
       </c>
       <c r="AA383">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB383">
         <v>8000</v>
@@ -35336,7 +35336,7 @@
         <v>172</v>
       </c>
       <c r="AA384">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="AB384">
         <v>8000</v>
@@ -35425,7 +35425,7 @@
         <v>172</v>
       </c>
       <c r="AA385">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB385">
         <v>8000</v>
@@ -35514,7 +35514,7 @@
         <v>172</v>
       </c>
       <c r="AA386">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB386">
         <v>8000</v>
@@ -35603,7 +35603,7 @@
         <v>172</v>
       </c>
       <c r="AA387">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB387">
         <v>8000</v>
@@ -35692,7 +35692,7 @@
         <v>172</v>
       </c>
       <c r="AA388">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB388">
         <v>8000</v>
@@ -35781,7 +35781,7 @@
         <v>172</v>
       </c>
       <c r="AA389">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB389">
         <v>8000</v>
@@ -35870,7 +35870,7 @@
         <v>172</v>
       </c>
       <c r="AA390">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB390">
         <v>8000</v>
@@ -35962,7 +35962,7 @@
         <v>172</v>
       </c>
       <c r="AA391">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB391">
         <v>8000</v>
@@ -36054,7 +36054,7 @@
         <v>172</v>
       </c>
       <c r="AA392">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB392">
         <v>8000</v>
@@ -36143,7 +36143,7 @@
         <v>172</v>
       </c>
       <c r="AA393">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB393">
         <v>8000</v>
@@ -36232,7 +36232,7 @@
         <v>172</v>
       </c>
       <c r="AA394">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="AB394">
         <v>8000</v>
@@ -39457,7 +39457,7 @@
         <v>172</v>
       </c>
       <c r="AA430">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB430">
         <v>8000</v>
@@ -39546,7 +39546,7 @@
         <v>172</v>
       </c>
       <c r="AA431">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB431">
         <v>8000</v>
@@ -39635,7 +39635,7 @@
         <v>172</v>
       </c>
       <c r="AA432">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB432">
         <v>8000</v>
@@ -39724,7 +39724,7 @@
         <v>172</v>
       </c>
       <c r="AA433">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB433">
         <v>8000</v>
@@ -39813,7 +39813,7 @@
         <v>172</v>
       </c>
       <c r="AA434">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB434">
         <v>8000</v>
@@ -39902,7 +39902,7 @@
         <v>172</v>
       </c>
       <c r="AA435">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB435">
         <v>8000</v>
@@ -39994,7 +39994,7 @@
         <v>172</v>
       </c>
       <c r="AA436">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB436">
         <v>8000</v>
@@ -40086,7 +40086,7 @@
         <v>172</v>
       </c>
       <c r="AA437">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB437">
         <v>8000</v>
@@ -40175,7 +40175,7 @@
         <v>172</v>
       </c>
       <c r="AA438">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB438">
         <v>8000</v>
@@ -40264,7 +40264,7 @@
         <v>172</v>
       </c>
       <c r="AA439">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AB439">
         <v>8000</v>
